--- a/research/traditional_assets/database/data/bermuda/bermuda_drugs_biotechnology.xlsx
+++ b/research/traditional_assets/database/data/bermuda/bermuda_drugs_biotechnology.xlsx
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="G2">
-        <v>-2.308080808080808</v>
+        <v>-0.4282485875706215</v>
       </c>
       <c r="H2">
-        <v>-7.828282828282828</v>
+        <v>-0.8717514124293786</v>
       </c>
       <c r="I2">
-        <v>-8.706660215078987</v>
+        <v>-0.1693469136499068</v>
       </c>
       <c r="J2">
-        <v>-8.706660215078987</v>
+        <v>-0.1693469136499068</v>
       </c>
       <c r="K2">
-        <v>-175.2</v>
+        <v>142.6</v>
       </c>
       <c r="L2">
-        <v>-8.848484848484848</v>
+        <v>0.8056497175141243</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.801</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.0007690092165898619</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0.005617110799438991</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -621,76 +621,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.801</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>190.2</v>
+        <v>175.8</v>
       </c>
       <c r="V2">
-        <v>0.234583127775037</v>
+        <v>0.168778801843318</v>
       </c>
       <c r="W2">
-        <v>-0.4887029288702929</v>
+        <v>0.6663551401869159</v>
       </c>
       <c r="X2">
-        <v>0.06883557224890759</v>
+        <v>0.1318464546393186</v>
       </c>
       <c r="Y2">
-        <v>-0.5575385011192004</v>
+        <v>0.5345086855475973</v>
       </c>
       <c r="Z2">
-        <v>0.0708004191544593</v>
+        <v>5.985387826000651</v>
       </c>
       <c r="AA2">
-        <v>-0.616435192663047</v>
+        <v>-1.013606955330936</v>
       </c>
       <c r="AB2">
-        <v>0.06854506955393624</v>
+        <v>0.1314800185159064</v>
       </c>
       <c r="AC2">
-        <v>-0.6849802622169833</v>
+        <v>-1.145086973846842</v>
       </c>
       <c r="AD2">
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>7.059361292819638</v>
+        <v>5.772018580167553</v>
       </c>
       <c r="AF2">
-        <v>7.059361292819638</v>
+        <v>5.772018580167553</v>
       </c>
       <c r="AG2">
-        <v>-183.1406387071804</v>
+        <v>-170.0279814198325</v>
       </c>
       <c r="AH2">
-        <v>0.00863151004551767</v>
+        <v>0.005510953584565096</v>
       </c>
       <c r="AI2">
-        <v>0.03193423364445837</v>
+        <v>0.01480870433232594</v>
       </c>
       <c r="AJ2">
-        <v>-0.2917834895825611</v>
+        <v>-0.1950819643072252</v>
       </c>
       <c r="AK2">
-        <v>-5.934686624567098</v>
+        <v>-0.7946271785819001</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.05</v>
+        <v>-0.536</v>
       </c>
       <c r="AN2">
         <v>-0</v>
       </c>
       <c r="AP2">
-        <v>1.085728235162321</v>
+        <v>6.460029689203361</v>
       </c>
       <c r="AQ2">
-        <v>3468</v>
+        <v>60.44776119402984</v>
       </c>
     </row>
     <row r="3">
@@ -710,31 +713,31 @@
         </is>
       </c>
       <c r="G3">
-        <v>-2.308080808080808</v>
+        <v>-0.4282485875706215</v>
       </c>
       <c r="H3">
-        <v>-7.828282828282828</v>
+        <v>-0.8717514124293786</v>
       </c>
       <c r="I3">
-        <v>-8.706660215078987</v>
+        <v>-0.1693469136499068</v>
       </c>
       <c r="J3">
-        <v>-8.706660215078987</v>
+        <v>-0.1693469136499068</v>
       </c>
       <c r="K3">
-        <v>-175.2</v>
+        <v>142.6</v>
       </c>
       <c r="L3">
-        <v>-8.848484848484848</v>
+        <v>0.8056497175141243</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.801</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.0007690092165898619</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.005617110799438991</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -743,76 +746,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.801</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>190.2</v>
+        <v>175.8</v>
       </c>
       <c r="V3">
-        <v>0.234583127775037</v>
+        <v>0.168778801843318</v>
       </c>
       <c r="W3">
-        <v>-0.4887029288702929</v>
+        <v>0.6663551401869159</v>
       </c>
       <c r="X3">
-        <v>0.06883557224890759</v>
+        <v>0.1318464546393186</v>
       </c>
       <c r="Y3">
-        <v>-0.5575385011192004</v>
+        <v>0.5345086855475973</v>
       </c>
       <c r="Z3">
-        <v>0.0708004191544593</v>
+        <v>5.985387826000651</v>
       </c>
       <c r="AA3">
-        <v>-0.616435192663047</v>
+        <v>-1.013606955330936</v>
       </c>
       <c r="AB3">
-        <v>0.06854506955393624</v>
+        <v>0.1314800185159064</v>
       </c>
       <c r="AC3">
-        <v>-0.6849802622169833</v>
+        <v>-1.145086973846842</v>
       </c>
       <c r="AD3">
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>7.059361292819638</v>
+        <v>5.772018580167553</v>
       </c>
       <c r="AF3">
-        <v>7.059361292819638</v>
+        <v>5.772018580167553</v>
       </c>
       <c r="AG3">
-        <v>-183.1406387071804</v>
+        <v>-170.0279814198325</v>
       </c>
       <c r="AH3">
-        <v>0.00863151004551767</v>
+        <v>0.005510953584565096</v>
       </c>
       <c r="AI3">
-        <v>0.03193423364445837</v>
+        <v>0.01480870433232594</v>
       </c>
       <c r="AJ3">
-        <v>-0.2917834895825611</v>
+        <v>-0.1950819643072252</v>
       </c>
       <c r="AK3">
-        <v>-5.934686624567098</v>
+        <v>-0.7946271785819001</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.05</v>
+        <v>-0.536</v>
       </c>
       <c r="AN3">
         <v>-0</v>
       </c>
       <c r="AP3">
-        <v>1.085728235162321</v>
+        <v>6.460029689203361</v>
       </c>
       <c r="AQ3">
-        <v>3468</v>
+        <v>60.44776119402984</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/bermuda/bermuda_drugs_biotechnology.xlsx
+++ b/research/traditional_assets/database/data/bermuda/bermuda_drugs_biotechnology.xlsx
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.4282485875706215</v>
+        <v>0.3321270607157218</v>
       </c>
       <c r="H2">
-        <v>-0.8717514124293786</v>
+        <v>0.04905508644953759</v>
       </c>
       <c r="I2">
-        <v>-0.1693469136499068</v>
+        <v>-0.06762885404434597</v>
       </c>
       <c r="J2">
-        <v>-0.1693469136499068</v>
+        <v>-0.06762885404434597</v>
       </c>
       <c r="K2">
-        <v>142.6</v>
+        <v>-6.69</v>
       </c>
       <c r="L2">
-        <v>0.8056497175141243</v>
+        <v>-0.02689987937273824</v>
       </c>
       <c r="M2">
-        <v>0.801</v>
+        <v>2.04</v>
       </c>
       <c r="N2">
-        <v>0.0007690092165898619</v>
+        <v>0.001653562454405447</v>
       </c>
       <c r="O2">
-        <v>0.005617110799438991</v>
+        <v>-0.304932735426009</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -621,79 +621,76 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2">
-        <v>0.801</v>
+        <v>2.04</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
       <c r="U2">
-        <v>175.8</v>
+        <v>117.8</v>
       </c>
       <c r="V2">
-        <v>0.168778801843318</v>
+        <v>0.09548512604360865</v>
       </c>
       <c r="W2">
-        <v>0.6663551401869159</v>
+        <v>-0.017421875</v>
       </c>
       <c r="X2">
-        <v>0.1318464546393186</v>
+        <v>0.1061885943725669</v>
       </c>
       <c r="Y2">
-        <v>0.5345086855475973</v>
+        <v>-0.1236104693725669</v>
       </c>
       <c r="Z2">
-        <v>5.985387826000651</v>
+        <v>1.162711981025501</v>
       </c>
       <c r="AA2">
-        <v>-1.013606955330936</v>
+        <v>-0.07863287886038597</v>
       </c>
       <c r="AB2">
-        <v>0.1314800185159064</v>
+        <v>0.1059766447374849</v>
       </c>
       <c r="AC2">
-        <v>-1.145086973846842</v>
+        <v>-0.1846095235978709</v>
       </c>
       <c r="AD2">
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>5.772018580167553</v>
+        <v>5.69648000414422</v>
       </c>
       <c r="AF2">
-        <v>5.772018580167553</v>
+        <v>5.69648000414422</v>
       </c>
       <c r="AG2">
-        <v>-170.0279814198325</v>
+        <v>-112.1035199958558</v>
       </c>
       <c r="AH2">
-        <v>0.005510953584565096</v>
+        <v>0.004596172488827121</v>
       </c>
       <c r="AI2">
-        <v>0.01480870433232594</v>
+        <v>0.01386691532528894</v>
       </c>
       <c r="AJ2">
-        <v>-0.1950819643072252</v>
+        <v>-0.09994995704287656</v>
       </c>
       <c r="AK2">
-        <v>-0.7946271785819001</v>
+        <v>-0.3826104668365645</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.536</v>
+        <v>0</v>
       </c>
       <c r="AN2">
         <v>-0</v>
       </c>
       <c r="AP2">
-        <v>6.460029689203361</v>
-      </c>
-      <c r="AQ2">
-        <v>60.44776119402984</v>
+        <v>8.441530120169862</v>
       </c>
     </row>
     <row r="3">
@@ -713,31 +710,31 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.4282485875706215</v>
+        <v>0.3321270607157218</v>
       </c>
       <c r="H3">
-        <v>-0.8717514124293786</v>
+        <v>0.04905508644953759</v>
       </c>
       <c r="I3">
-        <v>-0.1693469136499068</v>
+        <v>-0.06762885404434597</v>
       </c>
       <c r="J3">
-        <v>-0.1693469136499068</v>
+        <v>-0.06762885404434597</v>
       </c>
       <c r="K3">
-        <v>142.6</v>
+        <v>-6.69</v>
       </c>
       <c r="L3">
-        <v>0.8056497175141243</v>
+        <v>-0.02689987937273824</v>
       </c>
       <c r="M3">
-        <v>0.801</v>
+        <v>2.04</v>
       </c>
       <c r="N3">
-        <v>0.0007690092165898619</v>
+        <v>0.001653562454405447</v>
       </c>
       <c r="O3">
-        <v>0.005617110799438991</v>
+        <v>-0.304932735426009</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -746,79 +743,76 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>0.801</v>
+        <v>2.04</v>
       </c>
       <c r="T3">
         <v>1</v>
       </c>
       <c r="U3">
-        <v>175.8</v>
+        <v>117.8</v>
       </c>
       <c r="V3">
-        <v>0.168778801843318</v>
+        <v>0.09548512604360865</v>
       </c>
       <c r="W3">
-        <v>0.6663551401869159</v>
+        <v>-0.017421875</v>
       </c>
       <c r="X3">
-        <v>0.1318464546393186</v>
+        <v>0.1061885943725669</v>
       </c>
       <c r="Y3">
-        <v>0.5345086855475973</v>
+        <v>-0.1236104693725669</v>
       </c>
       <c r="Z3">
-        <v>5.985387826000651</v>
+        <v>1.162711981025501</v>
       </c>
       <c r="AA3">
-        <v>-1.013606955330936</v>
+        <v>-0.07863287886038597</v>
       </c>
       <c r="AB3">
-        <v>0.1314800185159064</v>
+        <v>0.1059766447374849</v>
       </c>
       <c r="AC3">
-        <v>-1.145086973846842</v>
+        <v>-0.1846095235978709</v>
       </c>
       <c r="AD3">
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>5.772018580167553</v>
+        <v>5.69648000414422</v>
       </c>
       <c r="AF3">
-        <v>5.772018580167553</v>
+        <v>5.69648000414422</v>
       </c>
       <c r="AG3">
-        <v>-170.0279814198325</v>
+        <v>-112.1035199958558</v>
       </c>
       <c r="AH3">
-        <v>0.005510953584565096</v>
+        <v>0.004596172488827121</v>
       </c>
       <c r="AI3">
-        <v>0.01480870433232594</v>
+        <v>0.01386691532528894</v>
       </c>
       <c r="AJ3">
-        <v>-0.1950819643072252</v>
+        <v>-0.09994995704287656</v>
       </c>
       <c r="AK3">
-        <v>-0.7946271785819001</v>
+        <v>-0.3826104668365645</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.536</v>
+        <v>0</v>
       </c>
       <c r="AN3">
         <v>-0</v>
       </c>
       <c r="AP3">
-        <v>6.460029689203361</v>
-      </c>
-      <c r="AQ3">
-        <v>60.44776119402984</v>
+        <v>8.441530120169862</v>
       </c>
     </row>
   </sheetData>
